--- a/inst/extdata/additional_govdata.xlsx
+++ b/inst/extdata/additional_govdata.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\au785183\git_projects\bundeslaendeR\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2320DA3E-1B77-4E99-8892-8A0909057902}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E95BAFD-341E-4D39-8495-BD19A70D25C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1304" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1324" uniqueCount="273">
   <si>
     <t>gov_id</t>
   </si>
@@ -844,6 +844,15 @@
   </si>
   <si>
     <t>https://de.wikipedia.org/wiki/Kabinett_Lies</t>
+  </si>
+  <si>
+    <t>2026-01-06</t>
+  </si>
+  <si>
+    <t>2026-01-28</t>
+  </si>
+  <si>
+    <t>https://de.wikipedia.org/wiki/Kabinett_Schulze</t>
   </si>
 </sst>
 </file>
@@ -1162,7 +1171,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I260"/>
+  <dimension ref="A1:I264"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="19.140625" customWidth="1"/>
@@ -3076,7 +3085,7 @@
         <v>262</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>24</v>
+        <v>270</v>
       </c>
       <c r="G66" t="s">
         <v>20</v>
@@ -3105,7 +3114,7 @@
         <v>262</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>24</v>
+        <v>270</v>
       </c>
       <c r="G67" t="s">
         <v>260</v>
@@ -3119,31 +3128,31 @@
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>10620</v>
+        <v>10512</v>
       </c>
       <c r="B68" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="C68">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D68">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>73</v>
+        <v>270</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>75</v>
+        <v>24</v>
       </c>
       <c r="G68" t="s">
         <v>20</v>
       </c>
       <c r="H68">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I68" t="s">
-        <v>71</v>
+        <v>263</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
@@ -3166,10 +3175,10 @@
         <v>75</v>
       </c>
       <c r="G69" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="H69">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I69" t="s">
         <v>71</v>
@@ -3195,10 +3204,10 @@
         <v>75</v>
       </c>
       <c r="G70" t="s">
-        <v>230</v>
+        <v>11</v>
       </c>
       <c r="H70">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I70" t="s">
         <v>71</v>
@@ -3206,7 +3215,7 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>10621</v>
+        <v>10620</v>
       </c>
       <c r="B71" t="s">
         <v>72</v>
@@ -3215,19 +3224,19 @@
         <v>0</v>
       </c>
       <c r="D71">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E71" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F71" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="F71" s="1" t="s">
-        <v>74</v>
-      </c>
       <c r="G71" t="s">
-        <v>20</v>
+        <v>230</v>
       </c>
       <c r="H71">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I71" t="s">
         <v>71</v>
@@ -3253,10 +3262,10 @@
         <v>74</v>
       </c>
       <c r="G72" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="H72">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I72" t="s">
         <v>71</v>
@@ -3264,31 +3273,31 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>10619</v>
+        <v>10621</v>
       </c>
       <c r="B73" t="s">
         <v>72</v>
       </c>
       <c r="C73">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D73">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G73" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H73">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I73" t="s">
-        <v>14</v>
+        <v>71</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
@@ -3311,10 +3320,10 @@
         <v>77</v>
       </c>
       <c r="G74" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H74">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I74" t="s">
         <v>14</v>
@@ -3322,7 +3331,7 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>10622</v>
+        <v>10619</v>
       </c>
       <c r="B75" t="s">
         <v>72</v>
@@ -3331,22 +3340,22 @@
         <v>15</v>
       </c>
       <c r="D75">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E75" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F75" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="F75" s="1" t="s">
-        <v>78</v>
-      </c>
       <c r="G75" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H75">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I75" t="s">
-        <v>79</v>
+        <v>14</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
@@ -3369,10 +3378,10 @@
         <v>78</v>
       </c>
       <c r="G76" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H76">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I76" t="s">
         <v>79</v>
@@ -3380,31 +3389,31 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>10623</v>
+        <v>10622</v>
       </c>
       <c r="B77" t="s">
         <v>72</v>
       </c>
       <c r="C77">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D77">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E77" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F77" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="F77" s="1" t="s">
-        <v>81</v>
-      </c>
       <c r="G77" t="s">
         <v>20</v>
       </c>
       <c r="H77">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I77" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
@@ -3427,10 +3436,10 @@
         <v>81</v>
       </c>
       <c r="G78" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H78">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I78" t="s">
         <v>80</v>
@@ -3438,31 +3447,31 @@
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>10624</v>
+        <v>10623</v>
       </c>
       <c r="B79" t="s">
         <v>72</v>
       </c>
       <c r="C79">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D79">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E79" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F79" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="F79" s="1" t="s">
-        <v>82</v>
-      </c>
       <c r="G79" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H79">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I79" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
@@ -3485,10 +3494,10 @@
         <v>82</v>
       </c>
       <c r="G80" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H80">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I80" t="s">
         <v>83</v>
@@ -3496,31 +3505,31 @@
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>10625</v>
+        <v>10624</v>
       </c>
       <c r="B81" t="s">
         <v>72</v>
       </c>
       <c r="C81">
+        <v>17</v>
+      </c>
+      <c r="D81">
+        <v>22</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G81" t="s">
         <v>18</v>
       </c>
-      <c r="D81">
-        <v>23</v>
-      </c>
-      <c r="E81" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="F81" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="G81" t="s">
-        <v>20</v>
-      </c>
       <c r="H81">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I81" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
@@ -3543,10 +3552,10 @@
         <v>84</v>
       </c>
       <c r="G82" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H82">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I82" t="s">
         <v>85</v>
@@ -3554,31 +3563,31 @@
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83">
-        <v>10626</v>
+        <v>10625</v>
       </c>
       <c r="B83" t="s">
         <v>72</v>
       </c>
       <c r="C83">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D83">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E83" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F83" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="F83" s="1" t="s">
-        <v>250</v>
-      </c>
       <c r="G83" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H83">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I83" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
@@ -3601,10 +3610,10 @@
         <v>250</v>
       </c>
       <c r="G84" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H84">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I84" t="s">
         <v>86</v>
@@ -3630,10 +3639,10 @@
         <v>250</v>
       </c>
       <c r="G85" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="H85">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I85" t="s">
         <v>86</v>
@@ -3641,31 +3650,31 @@
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86">
-        <v>10627</v>
+        <v>10626</v>
       </c>
       <c r="B86" t="s">
         <v>72</v>
       </c>
       <c r="C86">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D86">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E86" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F86" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="F86" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="G86" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="H86">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I86" t="s">
-        <v>251</v>
+        <v>86</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
@@ -3688,10 +3697,10 @@
         <v>24</v>
       </c>
       <c r="G87" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H87">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I87" t="s">
         <v>251</v>
@@ -3717,7 +3726,7 @@
         <v>24</v>
       </c>
       <c r="G88" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="H88">
         <v>2</v>
@@ -3728,89 +3737,89 @@
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89">
-        <v>10720</v>
+        <v>10627</v>
       </c>
       <c r="B89" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="C89">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D89">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>88</v>
+        <v>250</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>92</v>
+        <v>24</v>
       </c>
       <c r="G89" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="H89">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="I89" t="s">
-        <v>14</v>
+        <v>251</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90">
-        <v>10721</v>
+        <v>10720</v>
       </c>
       <c r="B90" t="s">
         <v>87</v>
       </c>
       <c r="C90">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D90">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E90" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F90" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="F90" s="1" t="s">
-        <v>89</v>
-      </c>
       <c r="G90" t="s">
         <v>10</v>
       </c>
       <c r="H90">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I90" t="s">
-        <v>93</v>
+        <v>14</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91">
-        <v>10722</v>
+        <v>10721</v>
       </c>
       <c r="B91" t="s">
         <v>87</v>
       </c>
       <c r="C91">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D91">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E91" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F91" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="F91" s="1" t="s">
-        <v>90</v>
-      </c>
       <c r="G91" t="s">
         <v>10</v>
       </c>
       <c r="H91">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I91" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
@@ -3833,10 +3842,10 @@
         <v>90</v>
       </c>
       <c r="G92" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H92">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I92" t="s">
         <v>91</v>
@@ -3844,7 +3853,7 @@
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93">
-        <v>10723</v>
+        <v>10722</v>
       </c>
       <c r="B93" t="s">
         <v>87</v>
@@ -3853,22 +3862,22 @@
         <v>18</v>
       </c>
       <c r="D93">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E93" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F93" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="F93" s="1" t="s">
-        <v>95</v>
-      </c>
       <c r="G93" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H93">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I93" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
@@ -3891,10 +3900,10 @@
         <v>95</v>
       </c>
       <c r="G94" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H94">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I94" t="s">
         <v>94</v>
@@ -3902,31 +3911,31 @@
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95">
-        <v>10724</v>
+        <v>10723</v>
       </c>
       <c r="B95" t="s">
         <v>87</v>
       </c>
       <c r="C95">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D95">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E95" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F95" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="F95" s="1" t="s">
-        <v>96</v>
-      </c>
       <c r="G95" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H95">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I95" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
@@ -3949,10 +3958,10 @@
         <v>96</v>
       </c>
       <c r="G96" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="H96">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I96" t="s">
         <v>97</v>
@@ -3960,31 +3969,31 @@
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97">
-        <v>10725</v>
+        <v>10724</v>
       </c>
       <c r="B97" t="s">
         <v>87</v>
       </c>
       <c r="C97">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D97">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E97" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="F97" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="F97" s="1" t="s">
-        <v>241</v>
-      </c>
       <c r="G97" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="H97">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I97" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
@@ -4007,10 +4016,10 @@
         <v>241</v>
       </c>
       <c r="G98" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="H98">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I98" t="s">
         <v>98</v>
@@ -4018,7 +4027,7 @@
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99">
-        <v>10726</v>
+        <v>10725</v>
       </c>
       <c r="B99" t="s">
         <v>87</v>
@@ -4027,22 +4036,22 @@
         <v>20</v>
       </c>
       <c r="D99">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E99" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F99" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="F99" s="1" t="s">
-        <v>254</v>
-      </c>
       <c r="G99" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="H99">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I99" t="s">
-        <v>242</v>
+        <v>98</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
@@ -4065,10 +4074,10 @@
         <v>254</v>
       </c>
       <c r="G100" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="H100">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I100" t="s">
         <v>242</v>
@@ -4076,31 +4085,31 @@
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101">
-        <v>10727</v>
+        <v>10726</v>
       </c>
       <c r="B101" t="s">
         <v>87</v>
       </c>
       <c r="C101">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D101">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E101" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="F101" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="F101" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="G101" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="H101">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I101" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
@@ -4123,10 +4132,10 @@
         <v>24</v>
       </c>
       <c r="G102" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H102">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I102" t="s">
         <v>255</v>
@@ -4134,60 +4143,60 @@
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103">
-        <v>10826</v>
+        <v>10727</v>
       </c>
       <c r="B103" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="C103">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D103">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>100</v>
+        <v>254</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>102</v>
+        <v>24</v>
       </c>
       <c r="G103" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H103">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I103" t="s">
-        <v>14</v>
+        <v>255</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104">
-        <v>10827</v>
+        <v>10826</v>
       </c>
       <c r="B104" t="s">
         <v>99</v>
       </c>
       <c r="C104">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D104">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E104" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F104" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="F104" s="1" t="s">
-        <v>103</v>
-      </c>
       <c r="G104" t="s">
         <v>10</v>
       </c>
       <c r="H104">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I104" t="s">
-        <v>101</v>
+        <v>14</v>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
@@ -4210,10 +4219,10 @@
         <v>103</v>
       </c>
       <c r="G105" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="H105">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I105" t="s">
         <v>101</v>
@@ -4221,7 +4230,7 @@
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106">
-        <v>10828</v>
+        <v>10827</v>
       </c>
       <c r="B106" t="s">
         <v>99</v>
@@ -4230,22 +4239,22 @@
         <v>19</v>
       </c>
       <c r="D106">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E106" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F106" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="F106" s="1" t="s">
-        <v>104</v>
-      </c>
       <c r="G106" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="H106">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I106" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">
@@ -4268,10 +4277,10 @@
         <v>104</v>
       </c>
       <c r="G107" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="H107">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I107" t="s">
         <v>105</v>
@@ -4279,7 +4288,7 @@
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108">
-        <v>10829</v>
+        <v>10828</v>
       </c>
       <c r="B108" t="s">
         <v>99</v>
@@ -4288,19 +4297,19 @@
         <v>19</v>
       </c>
       <c r="D108">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E108" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="F108" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="F108" s="1" t="s">
-        <v>106</v>
-      </c>
       <c r="G108" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="H108">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I108" t="s">
         <v>105</v>
@@ -4308,60 +4317,60 @@
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109">
-        <v>10830</v>
+        <v>10829</v>
       </c>
       <c r="B109" t="s">
         <v>99</v>
       </c>
       <c r="C109">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D109">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E109" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="F109" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="F109" s="1" t="s">
-        <v>108</v>
-      </c>
       <c r="G109" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H109">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I109" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110">
-        <v>10831</v>
+        <v>10830</v>
       </c>
       <c r="B110" t="s">
         <v>99</v>
       </c>
       <c r="C110">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D110">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E110" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F110" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="F110" s="1" t="s">
-        <v>110</v>
-      </c>
       <c r="G110" t="s">
         <v>20</v>
       </c>
       <c r="H110">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I110" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
@@ -4384,10 +4393,10 @@
         <v>110</v>
       </c>
       <c r="G111" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H111">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I111" t="s">
         <v>109</v>
@@ -4395,7 +4404,7 @@
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112">
-        <v>10832</v>
+        <v>10831</v>
       </c>
       <c r="B112" t="s">
         <v>99</v>
@@ -4404,22 +4413,22 @@
         <v>21</v>
       </c>
       <c r="D112">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E112" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F112" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="F112" s="1" t="s">
-        <v>112</v>
-      </c>
       <c r="G112" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H112">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I112" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
@@ -4442,10 +4451,10 @@
         <v>112</v>
       </c>
       <c r="G113" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H113">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I113" t="s">
         <v>111</v>
@@ -4453,31 +4462,31 @@
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114">
-        <v>10833</v>
+        <v>10832</v>
       </c>
       <c r="B114" t="s">
         <v>99</v>
       </c>
       <c r="C114">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D114">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E114" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F114" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="F114" s="1" t="s">
-        <v>264</v>
-      </c>
       <c r="G114" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H114">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I114" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.25">
@@ -4500,10 +4509,10 @@
         <v>264</v>
       </c>
       <c r="G115" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H115">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I115" t="s">
         <v>113</v>
@@ -4511,31 +4520,31 @@
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116">
-        <v>10834</v>
+        <v>10833</v>
       </c>
       <c r="B116" t="s">
         <v>99</v>
       </c>
       <c r="C116">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D116">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E116" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="F116" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="F116" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="G116" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H116">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I116" t="s">
-        <v>265</v>
+        <v>113</v>
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
@@ -4558,10 +4567,10 @@
         <v>24</v>
       </c>
       <c r="G117" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H117">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I117" t="s">
         <v>265</v>
@@ -4569,31 +4578,31 @@
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118">
-        <v>10905</v>
+        <v>10834</v>
       </c>
       <c r="B118" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="C118">
+        <v>23</v>
+      </c>
+      <c r="D118">
+        <v>34</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="F118" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G118" t="s">
+        <v>18</v>
+      </c>
+      <c r="H118">
         <v>4</v>
       </c>
-      <c r="D118">
-        <v>5</v>
-      </c>
-      <c r="E118" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="F118" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="G118" t="s">
-        <v>20</v>
-      </c>
-      <c r="H118">
-        <v>6</v>
-      </c>
       <c r="I118" t="s">
-        <v>14</v>
+        <v>265</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
@@ -4616,10 +4625,10 @@
         <v>116</v>
       </c>
       <c r="G119" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="H119">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I119" t="s">
         <v>14</v>
@@ -4627,31 +4636,31 @@
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120">
-        <v>10906</v>
+        <v>10905</v>
       </c>
       <c r="B120" t="s">
         <v>114</v>
       </c>
       <c r="C120">
+        <v>4</v>
+      </c>
+      <c r="D120">
         <v>5</v>
       </c>
-      <c r="D120">
-        <v>6</v>
-      </c>
       <c r="E120" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F120" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="F120" s="1" t="s">
-        <v>117</v>
-      </c>
       <c r="G120" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="H120">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I120" t="s">
-        <v>118</v>
+        <v>14</v>
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
@@ -4674,10 +4683,10 @@
         <v>117</v>
       </c>
       <c r="G121" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H121">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I121" t="s">
         <v>118</v>
@@ -4685,7 +4694,7 @@
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122">
-        <v>10910</v>
+        <v>10906</v>
       </c>
       <c r="B122" t="s">
         <v>114</v>
@@ -4694,22 +4703,22 @@
         <v>5</v>
       </c>
       <c r="D122">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E122" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="F122" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="F122" s="1" t="s">
-        <v>119</v>
-      </c>
       <c r="G122" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H122">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I122" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
@@ -4732,10 +4741,10 @@
         <v>119</v>
       </c>
       <c r="G123" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H123">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I123" t="s">
         <v>120</v>
@@ -4743,31 +4752,31 @@
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124">
-        <v>10911</v>
+        <v>10910</v>
       </c>
       <c r="B124" t="s">
         <v>114</v>
       </c>
       <c r="C124">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D124">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E124" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F124" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="F124" s="1" t="s">
-        <v>121</v>
-      </c>
       <c r="G124" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H124">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I124" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.25">
@@ -4790,10 +4799,10 @@
         <v>121</v>
       </c>
       <c r="G125" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H125">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I125" t="s">
         <v>122</v>
@@ -4801,31 +4810,31 @@
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126">
-        <v>10912</v>
+        <v>10911</v>
       </c>
       <c r="B126" t="s">
         <v>114</v>
       </c>
       <c r="C126">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D126">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E126" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F126" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="F126" s="1" t="s">
-        <v>124</v>
-      </c>
       <c r="G126" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H126">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I126" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
@@ -4848,10 +4857,10 @@
         <v>124</v>
       </c>
       <c r="G127" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H127">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I127" t="s">
         <v>123</v>
@@ -4859,7 +4868,7 @@
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128">
-        <v>10913</v>
+        <v>10912</v>
       </c>
       <c r="B128" t="s">
         <v>114</v>
@@ -4868,22 +4877,22 @@
         <v>7</v>
       </c>
       <c r="D128">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E128" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F128" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="F128" s="1" t="s">
-        <v>233</v>
-      </c>
       <c r="G128" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H128">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I128" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.25">
@@ -4906,10 +4915,10 @@
         <v>233</v>
       </c>
       <c r="G129" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H129">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I129" t="s">
         <v>125</v>
@@ -4917,31 +4926,31 @@
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130">
-        <v>10914</v>
+        <v>10913</v>
       </c>
       <c r="B130" t="s">
         <v>114</v>
       </c>
       <c r="C130">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D130">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E130" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="F130" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="F130" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="G130" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H130">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I130" t="s">
-        <v>234</v>
+        <v>125</v>
       </c>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.25">
@@ -4964,10 +4973,10 @@
         <v>24</v>
       </c>
       <c r="G131" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="H131">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I131" t="s">
         <v>234</v>
@@ -4975,31 +4984,31 @@
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132">
-        <v>11027</v>
+        <v>10914</v>
       </c>
       <c r="B132" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="C132">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D132">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>128</v>
+        <v>233</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>129</v>
+        <v>24</v>
       </c>
       <c r="G132" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="H132">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I132" t="s">
-        <v>14</v>
+        <v>234</v>
       </c>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.25">
@@ -5022,10 +5031,10 @@
         <v>129</v>
       </c>
       <c r="G133" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H133">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I133" t="s">
         <v>14</v>
@@ -5033,31 +5042,31 @@
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134">
-        <v>11028</v>
+        <v>11027</v>
       </c>
       <c r="B134" t="s">
         <v>127</v>
       </c>
       <c r="C134">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D134">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E134" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F134" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="F134" s="1" t="s">
-        <v>130</v>
-      </c>
       <c r="G134" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H134">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I134" t="s">
-        <v>131</v>
+        <v>14</v>
       </c>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.25">
@@ -5080,10 +5089,10 @@
         <v>130</v>
       </c>
       <c r="G135" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H135">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I135" t="s">
         <v>131</v>
@@ -5091,7 +5100,7 @@
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136">
-        <v>11029</v>
+        <v>11028</v>
       </c>
       <c r="B136" t="s">
         <v>127</v>
@@ -5100,22 +5109,22 @@
         <v>16</v>
       </c>
       <c r="D136">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E136" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="F136" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="F136" s="1" t="s">
-        <v>132</v>
-      </c>
       <c r="G136" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H136">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I136" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.25">
@@ -5138,10 +5147,10 @@
         <v>132</v>
       </c>
       <c r="G137" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H137">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I137" t="s">
         <v>133</v>
@@ -5149,31 +5158,31 @@
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138">
-        <v>11030</v>
+        <v>11029</v>
       </c>
       <c r="B138" t="s">
         <v>127</v>
       </c>
       <c r="C138">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D138">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E138" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="F138" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="F138" s="1" t="s">
-        <v>134</v>
-      </c>
       <c r="G138" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="H138">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I138" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.25">
@@ -5196,10 +5205,10 @@
         <v>134</v>
       </c>
       <c r="G139" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H139">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I139" t="s">
         <v>135</v>
@@ -5207,31 +5216,31 @@
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140">
-        <v>11031</v>
+        <v>11030</v>
       </c>
       <c r="B140" t="s">
         <v>127</v>
       </c>
       <c r="C140">
+        <v>17</v>
+      </c>
+      <c r="D140">
+        <v>30</v>
+      </c>
+      <c r="E140" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="F140" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="G140" t="s">
         <v>18</v>
       </c>
-      <c r="D140">
-        <v>31</v>
-      </c>
-      <c r="E140" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="F140" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="G140" t="s">
-        <v>20</v>
-      </c>
       <c r="H140">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I140" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.25">
@@ -5254,10 +5263,10 @@
         <v>246</v>
       </c>
       <c r="G141" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H141">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I141" t="s">
         <v>136</v>
@@ -5265,31 +5274,31 @@
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142">
-        <v>11032</v>
+        <v>11031</v>
       </c>
       <c r="B142" t="s">
         <v>127</v>
       </c>
       <c r="C142">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D142">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E142" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F142" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="F142" s="1" t="s">
-        <v>268</v>
-      </c>
       <c r="G142" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H142">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I142" t="s">
-        <v>247</v>
+        <v>136</v>
       </c>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.25">
@@ -5312,10 +5321,10 @@
         <v>268</v>
       </c>
       <c r="G143" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H143">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I143" t="s">
         <v>247</v>
@@ -5323,7 +5332,7 @@
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144">
-        <v>11033</v>
+        <v>11032</v>
       </c>
       <c r="B144" t="s">
         <v>127</v>
@@ -5332,22 +5341,22 @@
         <v>19</v>
       </c>
       <c r="D144">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E144" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="F144" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="F144" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="G144" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H144">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I144" t="s">
-        <v>269</v>
+        <v>247</v>
       </c>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.25">
@@ -5370,10 +5379,10 @@
         <v>24</v>
       </c>
       <c r="G145" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H145">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I145" t="s">
         <v>269</v>
@@ -5381,31 +5390,31 @@
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146">
-        <v>11122</v>
+        <v>11033</v>
       </c>
       <c r="B146" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="C146">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D146">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>138</v>
+        <v>268</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>139</v>
+        <v>24</v>
       </c>
       <c r="G146" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="H146">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I146" t="s">
-        <v>14</v>
+        <v>269</v>
       </c>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.25">
@@ -5428,10 +5437,10 @@
         <v>139</v>
       </c>
       <c r="G147" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H147">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I147" t="s">
         <v>14</v>
@@ -5439,31 +5448,31 @@
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148">
-        <v>11123</v>
+        <v>11122</v>
       </c>
       <c r="B148" t="s">
         <v>137</v>
       </c>
       <c r="C148">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D148">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E148" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="F148" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="F148" s="1" t="s">
-        <v>140</v>
-      </c>
       <c r="G148" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="H148">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I148" t="s">
-        <v>141</v>
+        <v>14</v>
       </c>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.25">
@@ -5486,10 +5495,10 @@
         <v>140</v>
       </c>
       <c r="G149" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H149">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I149" t="s">
         <v>141</v>
@@ -5497,31 +5506,31 @@
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150">
-        <v>11124</v>
+        <v>11123</v>
       </c>
       <c r="B150" t="s">
         <v>137</v>
       </c>
       <c r="C150">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D150">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E150" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="F150" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="F150" s="1" t="s">
-        <v>142</v>
-      </c>
       <c r="G150" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H150">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="I150" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.25">
@@ -5544,10 +5553,10 @@
         <v>142</v>
       </c>
       <c r="G151" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H151">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I151" t="s">
         <v>143</v>
@@ -5555,31 +5564,31 @@
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152">
-        <v>11125</v>
+        <v>11124</v>
       </c>
       <c r="B152" t="s">
         <v>137</v>
       </c>
       <c r="C152">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D152">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E152" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="F152" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="F152" s="1" t="s">
-        <v>235</v>
-      </c>
       <c r="G152" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="H152">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I152" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.25">
@@ -5602,10 +5611,10 @@
         <v>235</v>
       </c>
       <c r="G153" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H153">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I153" t="s">
         <v>144</v>
@@ -5613,7 +5622,7 @@
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154">
-        <v>11126</v>
+        <v>11125</v>
       </c>
       <c r="B154" t="s">
         <v>137</v>
@@ -5622,22 +5631,22 @@
         <v>17</v>
       </c>
       <c r="D154">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E154" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="F154" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="F154" s="1" t="s">
-        <v>243</v>
-      </c>
       <c r="G154" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H154">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I154" t="s">
-        <v>236</v>
+        <v>144</v>
       </c>
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.25">
@@ -5660,10 +5669,10 @@
         <v>243</v>
       </c>
       <c r="G155" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H155">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I155" t="s">
         <v>236</v>
@@ -5671,31 +5680,31 @@
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156">
-        <v>11127</v>
+        <v>11126</v>
       </c>
       <c r="B156" t="s">
         <v>137</v>
       </c>
       <c r="C156">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D156">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E156" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F156" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="F156" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="G156" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H156">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I156" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.25">
@@ -5718,10 +5727,10 @@
         <v>24</v>
       </c>
       <c r="G157" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="H157">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I157" t="s">
         <v>244</v>
@@ -5729,31 +5738,31 @@
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158">
-        <v>11221</v>
+        <v>11127</v>
       </c>
       <c r="B158" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="C158">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D158">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>146</v>
+        <v>243</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>147</v>
+        <v>24</v>
       </c>
       <c r="G158" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H158">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I158" t="s">
-        <v>14</v>
+        <v>244</v>
       </c>
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.25">
@@ -5776,10 +5785,10 @@
         <v>147</v>
       </c>
       <c r="G159" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="H159">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I159" t="s">
         <v>14</v>
@@ -5787,60 +5796,60 @@
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160">
-        <v>11222</v>
+        <v>11221</v>
       </c>
       <c r="B160" t="s">
         <v>145</v>
       </c>
       <c r="C160">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D160">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E160" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="F160" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="F160" s="1" t="s">
-        <v>148</v>
-      </c>
       <c r="G160" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="H160">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="I160" t="s">
-        <v>149</v>
+        <v>14</v>
       </c>
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161">
-        <v>11223</v>
+        <v>11222</v>
       </c>
       <c r="B161" t="s">
         <v>145</v>
       </c>
       <c r="C161">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D161">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E161" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="F161" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="F161" s="1" t="s">
-        <v>151</v>
-      </c>
       <c r="G161" t="s">
         <v>20</v>
       </c>
       <c r="H161">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I161" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.25">
@@ -5863,10 +5872,10 @@
         <v>151</v>
       </c>
       <c r="G162" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H162">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I162" t="s">
         <v>150</v>
@@ -5874,7 +5883,7 @@
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163">
-        <v>11224</v>
+        <v>11223</v>
       </c>
       <c r="B163" t="s">
         <v>145</v>
@@ -5883,22 +5892,22 @@
         <v>16</v>
       </c>
       <c r="D163">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E163" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="F163" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="F163" s="1" t="s">
-        <v>152</v>
-      </c>
       <c r="G163" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H163">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I163" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.25">
@@ -5921,10 +5930,10 @@
         <v>152</v>
       </c>
       <c r="G164" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H164">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I164" t="s">
         <v>153</v>
@@ -5932,31 +5941,31 @@
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165">
-        <v>11225</v>
+        <v>11224</v>
       </c>
       <c r="B165" t="s">
         <v>145</v>
       </c>
       <c r="C165">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D165">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E165" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="F165" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="F165" s="1" t="s">
-        <v>154</v>
-      </c>
       <c r="G165" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H165">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I165" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.25">
@@ -5979,10 +5988,10 @@
         <v>154</v>
       </c>
       <c r="G166" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="H166">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I166" t="s">
         <v>155</v>
@@ -6008,7 +6017,7 @@
         <v>154</v>
       </c>
       <c r="G167" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="H167">
         <v>2</v>
@@ -6019,31 +6028,31 @@
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168">
-        <v>11226</v>
+        <v>11225</v>
       </c>
       <c r="B168" t="s">
         <v>145</v>
       </c>
       <c r="C168">
+        <v>17</v>
+      </c>
+      <c r="D168">
+        <v>25</v>
+      </c>
+      <c r="E168" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="F168" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="G168" t="s">
         <v>18</v>
       </c>
-      <c r="D168">
-        <v>26</v>
-      </c>
-      <c r="E168" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="F168" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="G168" t="s">
-        <v>20</v>
-      </c>
       <c r="H168">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I168" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.25">
@@ -6066,10 +6075,10 @@
         <v>266</v>
       </c>
       <c r="G169" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="H169">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I169" t="s">
         <v>156</v>
@@ -6095,7 +6104,7 @@
         <v>266</v>
       </c>
       <c r="G170" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="H170">
         <v>2</v>
@@ -6106,7 +6115,7 @@
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171">
-        <v>11227</v>
+        <v>11226</v>
       </c>
       <c r="B171" t="s">
         <v>145</v>
@@ -6115,22 +6124,22 @@
         <v>18</v>
       </c>
       <c r="D171">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E171" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="F171" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="F171" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="G171" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H171">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I171" t="s">
-        <v>267</v>
+        <v>156</v>
       </c>
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.25">
@@ -6153,10 +6162,10 @@
         <v>24</v>
       </c>
       <c r="G172" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="H172">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I172" t="s">
         <v>267</v>
@@ -6182,7 +6191,7 @@
         <v>24</v>
       </c>
       <c r="G173" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="H173">
         <v>2</v>
@@ -6193,31 +6202,31 @@
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174">
-        <v>11314</v>
+        <v>11227</v>
       </c>
       <c r="B174" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="C174">
-        <v>-2</v>
+        <v>18</v>
       </c>
       <c r="D174">
-        <v>-9</v>
+        <v>27</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>161</v>
+        <v>266</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>162</v>
+        <v>24</v>
       </c>
       <c r="G174" t="s">
-        <v>159</v>
+        <v>18</v>
       </c>
       <c r="H174">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I174" t="s">
-        <v>158</v>
+        <v>267</v>
       </c>
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.25">
@@ -6240,10 +6249,10 @@
         <v>162</v>
       </c>
       <c r="G175" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H175">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I175" t="s">
         <v>158</v>
@@ -6251,7 +6260,7 @@
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176">
-        <v>11315</v>
+        <v>11314</v>
       </c>
       <c r="B176" t="s">
         <v>157</v>
@@ -6260,51 +6269,51 @@
         <v>-2</v>
       </c>
       <c r="D176">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="E176" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="F176" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="F176" s="1" t="s">
-        <v>163</v>
-      </c>
       <c r="G176" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H176">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I176" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177">
-        <v>11316</v>
+        <v>11315</v>
       </c>
       <c r="B177" t="s">
         <v>157</v>
       </c>
       <c r="C177">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D177">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="E177" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="F177" s="1" t="s">
         <v>163</v>
-      </c>
-      <c r="F177" s="1" t="s">
-        <v>165</v>
       </c>
       <c r="G177" t="s">
         <v>159</v>
       </c>
       <c r="H177">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I177" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.25">
@@ -6327,10 +6336,10 @@
         <v>165</v>
       </c>
       <c r="G178" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H178">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I178" t="s">
         <v>166</v>
@@ -6338,7 +6347,7 @@
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179">
-        <v>11317</v>
+        <v>11316</v>
       </c>
       <c r="B179" t="s">
         <v>157</v>
@@ -6347,27 +6356,27 @@
         <v>-1</v>
       </c>
       <c r="D179">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="E179" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="F179" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="F179" s="1" t="s">
-        <v>167</v>
-      </c>
       <c r="G179" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H179">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I179" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180">
-        <v>11318</v>
+        <v>11317</v>
       </c>
       <c r="B180" t="s">
         <v>157</v>
@@ -6376,51 +6385,51 @@
         <v>-1</v>
       </c>
       <c r="D180">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="E180" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="F180" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="F180" s="1" t="s">
-        <v>169</v>
-      </c>
       <c r="G180" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="H180">
         <v>6</v>
       </c>
       <c r="I180" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181">
-        <v>11319</v>
+        <v>11318</v>
       </c>
       <c r="B181" t="s">
         <v>157</v>
       </c>
       <c r="C181">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="D181">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="E181" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="F181" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="F181" s="1" t="s">
-        <v>174</v>
-      </c>
       <c r="G181" t="s">
-        <v>10</v>
+        <v>170</v>
       </c>
       <c r="H181">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I181" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.25">
@@ -6443,10 +6452,10 @@
         <v>174</v>
       </c>
       <c r="G182" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H182">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I182" t="s">
         <v>173</v>
@@ -6472,7 +6481,7 @@
         <v>174</v>
       </c>
       <c r="G183" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="H183">
         <v>1</v>
@@ -6483,7 +6492,7 @@
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184">
-        <v>11320</v>
+        <v>11319</v>
       </c>
       <c r="B184" t="s">
         <v>157</v>
@@ -6492,19 +6501,19 @@
         <v>0</v>
       </c>
       <c r="D184">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="E184" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F184" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="F184" s="1" t="s">
-        <v>172</v>
-      </c>
       <c r="G184" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H184">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I184" t="s">
         <v>173</v>
@@ -6530,10 +6539,10 @@
         <v>172</v>
       </c>
       <c r="G185" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H185">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I185" t="s">
         <v>173</v>
@@ -6541,7 +6550,7 @@
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186">
-        <v>11321</v>
+        <v>11320</v>
       </c>
       <c r="B186" t="s">
         <v>157</v>
@@ -6550,22 +6559,22 @@
         <v>0</v>
       </c>
       <c r="D186">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="E186" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="F186" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="F186" s="1" t="s">
-        <v>175</v>
-      </c>
       <c r="G186" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H186">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I186" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.25">
@@ -6588,10 +6597,10 @@
         <v>175</v>
       </c>
       <c r="G187" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H187">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I187" t="s">
         <v>176</v>
@@ -6617,10 +6626,10 @@
         <v>175</v>
       </c>
       <c r="G188" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="H188">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I188" t="s">
         <v>176</v>
@@ -6628,7 +6637,7 @@
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A189">
-        <v>11322</v>
+        <v>11321</v>
       </c>
       <c r="B189" t="s">
         <v>157</v>
@@ -6637,22 +6646,22 @@
         <v>0</v>
       </c>
       <c r="D189">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="E189" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="F189" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="F189" s="1" t="s">
-        <v>177</v>
-      </c>
       <c r="G189" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H189">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I189" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.25">
@@ -6675,10 +6684,10 @@
         <v>177</v>
       </c>
       <c r="G190" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H190">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I190" t="s">
         <v>178</v>
@@ -6704,10 +6713,10 @@
         <v>177</v>
       </c>
       <c r="G191" t="s">
-        <v>159</v>
+        <v>20</v>
       </c>
       <c r="H191">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I191" t="s">
         <v>178</v>
@@ -6715,7 +6724,7 @@
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A192">
-        <v>11323</v>
+        <v>11322</v>
       </c>
       <c r="B192" t="s">
         <v>157</v>
@@ -6724,22 +6733,22 @@
         <v>0</v>
       </c>
       <c r="D192">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E192" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="F192" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="F192" s="1" t="s">
-        <v>179</v>
-      </c>
       <c r="G192" t="s">
-        <v>10</v>
+        <v>159</v>
       </c>
       <c r="H192">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I192" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.25">
@@ -6762,10 +6771,10 @@
         <v>179</v>
       </c>
       <c r="G193" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H193">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I193" t="s">
         <v>180</v>
@@ -6773,60 +6782,60 @@
     </row>
     <row r="194" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A194">
-        <v>11313</v>
+        <v>11323</v>
       </c>
       <c r="B194" t="s">
         <v>157</v>
       </c>
       <c r="C194">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D194">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="G194" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H194">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I194" t="s">
-        <v>14</v>
+        <v>180</v>
       </c>
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A195">
-        <v>11324</v>
+        <v>11313</v>
       </c>
       <c r="B195" t="s">
         <v>157</v>
       </c>
       <c r="C195">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D195">
+        <v>13</v>
+      </c>
+      <c r="E195" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="F195" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="G195" t="s">
+        <v>10</v>
+      </c>
+      <c r="H195">
+        <v>8</v>
+      </c>
+      <c r="I195" t="s">
         <v>14</v>
-      </c>
-      <c r="E195" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="F195" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="G195" t="s">
-        <v>10</v>
-      </c>
-      <c r="H195">
-        <v>5</v>
-      </c>
-      <c r="I195" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.25">
@@ -6849,10 +6858,10 @@
         <v>183</v>
       </c>
       <c r="G196" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H196">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I196" t="s">
         <v>184</v>
@@ -6878,7 +6887,7 @@
         <v>183</v>
       </c>
       <c r="G197" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="H197">
         <v>2</v>
@@ -6889,7 +6898,7 @@
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A198">
-        <v>11325</v>
+        <v>11324</v>
       </c>
       <c r="B198" t="s">
         <v>157</v>
@@ -6898,22 +6907,22 @@
         <v>11</v>
       </c>
       <c r="D198">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E198" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="F198" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="F198" s="1" t="s">
-        <v>185</v>
-      </c>
       <c r="G198" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="H198">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I198" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.25">
@@ -6936,10 +6945,10 @@
         <v>185</v>
       </c>
       <c r="G199" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H199">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I199" t="s">
         <v>186</v>
@@ -6965,7 +6974,7 @@
         <v>185</v>
       </c>
       <c r="G200" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="H200">
         <v>2</v>
@@ -6976,7 +6985,7 @@
     </row>
     <row r="201" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A201">
-        <v>11326</v>
+        <v>11325</v>
       </c>
       <c r="B201" t="s">
         <v>157</v>
@@ -6985,19 +6994,19 @@
         <v>11</v>
       </c>
       <c r="D201">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E201" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="F201" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="F201" s="1" t="s">
-        <v>187</v>
-      </c>
       <c r="G201" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="H201">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I201" t="s">
         <v>186</v>
@@ -7005,31 +7014,31 @@
     </row>
     <row r="202" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A202">
-        <v>11327</v>
+        <v>11326</v>
       </c>
       <c r="B202" t="s">
         <v>157</v>
       </c>
       <c r="C202">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D202">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E202" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="F202" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="F202" s="1" t="s">
-        <v>188</v>
-      </c>
       <c r="G202" t="s">
         <v>10</v>
       </c>
       <c r="H202">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I202" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.25">
@@ -7052,7 +7061,7 @@
         <v>188</v>
       </c>
       <c r="G203" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H203">
         <v>4</v>
@@ -7063,31 +7072,31 @@
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A204">
-        <v>11328</v>
+        <v>11327</v>
       </c>
       <c r="B204" t="s">
         <v>157</v>
       </c>
       <c r="C204">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D204">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E204" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="F204" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="F204" s="1" t="s">
-        <v>190</v>
-      </c>
       <c r="G204" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H204">
         <v>4</v>
       </c>
       <c r="I204" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.25">
@@ -7110,10 +7119,10 @@
         <v>190</v>
       </c>
       <c r="G205" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H205">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I205" t="s">
         <v>191</v>
@@ -7121,7 +7130,7 @@
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A206">
-        <v>11329</v>
+        <v>11328</v>
       </c>
       <c r="B206" t="s">
         <v>157</v>
@@ -7130,22 +7139,22 @@
         <v>13</v>
       </c>
       <c r="D206">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E206" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="F206" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="F206" s="1" t="s">
-        <v>240</v>
-      </c>
       <c r="G206" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H206">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I206" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.25">
@@ -7168,10 +7177,10 @@
         <v>240</v>
       </c>
       <c r="G207" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H207">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I207" t="s">
         <v>192</v>
@@ -7179,60 +7188,60 @@
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A208">
-        <v>11330</v>
+        <v>11329</v>
       </c>
       <c r="B208" t="s">
         <v>157</v>
       </c>
       <c r="C208">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D208">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E208" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F208" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="F208" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="G208" t="s">
         <v>20</v>
       </c>
       <c r="H208">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I208" t="s">
-        <v>239</v>
+        <v>192</v>
       </c>
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209">
-        <v>11405</v>
+        <v>11330</v>
       </c>
       <c r="B209" t="s">
-        <v>193</v>
+        <v>157</v>
       </c>
       <c r="C209">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D209">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>194</v>
+        <v>240</v>
       </c>
       <c r="F209" s="1" t="s">
-        <v>195</v>
+        <v>24</v>
       </c>
       <c r="G209" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H209">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I209" t="s">
-        <v>14</v>
+        <v>239</v>
       </c>
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.25">
@@ -7255,10 +7264,10 @@
         <v>195</v>
       </c>
       <c r="G210" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H210">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I210" t="s">
         <v>14</v>
@@ -7266,7 +7275,7 @@
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211">
-        <v>11406</v>
+        <v>11405</v>
       </c>
       <c r="B211" t="s">
         <v>193</v>
@@ -7275,22 +7284,22 @@
         <v>4</v>
       </c>
       <c r="D211">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E211" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="F211" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="F211" s="1" t="s">
-        <v>196</v>
-      </c>
       <c r="G211" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H211">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I211" t="s">
-        <v>199</v>
+        <v>14</v>
       </c>
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.25">
@@ -7313,10 +7322,10 @@
         <v>196</v>
       </c>
       <c r="G212" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H212">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I212" t="s">
         <v>199</v>
@@ -7324,31 +7333,31 @@
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213">
-        <v>11407</v>
+        <v>11406</v>
       </c>
       <c r="B213" t="s">
         <v>193</v>
       </c>
       <c r="C213">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D213">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E213" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="F213" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="F213" s="1" t="s">
-        <v>197</v>
-      </c>
       <c r="G213" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H213">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I213" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.25">
@@ -7371,10 +7380,10 @@
         <v>197</v>
       </c>
       <c r="G214" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H214">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I214" t="s">
         <v>198</v>
@@ -7382,31 +7391,31 @@
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215">
-        <v>11408</v>
+        <v>11407</v>
       </c>
       <c r="B215" t="s">
         <v>193</v>
       </c>
       <c r="C215">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D215">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E215" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="F215" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="F215" s="1" t="s">
-        <v>200</v>
-      </c>
       <c r="G215" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H215">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I215" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.25">
@@ -7429,10 +7438,10 @@
         <v>200</v>
       </c>
       <c r="G216" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H216">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I216" t="s">
         <v>201</v>
@@ -7440,7 +7449,7 @@
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217">
-        <v>11409</v>
+        <v>11408</v>
       </c>
       <c r="B217" t="s">
         <v>193</v>
@@ -7449,22 +7458,22 @@
         <v>6</v>
       </c>
       <c r="D217">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E217" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F217" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="F217" s="1" t="s">
-        <v>202</v>
-      </c>
       <c r="G217" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H217">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I217" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.25">
@@ -7487,10 +7496,10 @@
         <v>202</v>
       </c>
       <c r="G218" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H218">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I218" t="s">
         <v>203</v>
@@ -7498,31 +7507,31 @@
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A219">
-        <v>11410</v>
+        <v>11409</v>
       </c>
       <c r="B219" t="s">
         <v>193</v>
       </c>
       <c r="C219">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D219">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E219" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="F219" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="F219" s="1" t="s">
-        <v>256</v>
-      </c>
       <c r="G219" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H219">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I219" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.25">
@@ -7545,10 +7554,10 @@
         <v>256</v>
       </c>
       <c r="G220" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="H220">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I220" t="s">
         <v>204</v>
@@ -7574,7 +7583,7 @@
         <v>256</v>
       </c>
       <c r="G221" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H221">
         <v>2</v>
@@ -7585,31 +7594,31 @@
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A222">
-        <v>11411</v>
+        <v>11410</v>
       </c>
       <c r="B222" t="s">
         <v>193</v>
       </c>
       <c r="C222">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D222">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E222" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="F222" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="F222" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="G222" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H222">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I222" t="s">
-        <v>257</v>
+        <v>204</v>
       </c>
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.25">
@@ -7632,10 +7641,10 @@
         <v>24</v>
       </c>
       <c r="G223" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H223">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I223" t="s">
         <v>257</v>
@@ -7643,31 +7652,31 @@
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224">
-        <v>11506</v>
+        <v>11411</v>
       </c>
       <c r="B224" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="C224">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D224">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>206</v>
+        <v>256</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>207</v>
+        <v>24</v>
       </c>
       <c r="G224" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H224">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I224" t="s">
-        <v>14</v>
+        <v>257</v>
       </c>
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.25">
@@ -7690,10 +7699,10 @@
         <v>207</v>
       </c>
       <c r="G225" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H225">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I225" t="s">
         <v>14</v>
@@ -7701,31 +7710,31 @@
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A226">
-        <v>11507</v>
+        <v>11506</v>
       </c>
       <c r="B226" t="s">
         <v>205</v>
       </c>
       <c r="C226">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D226">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E226" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="F226" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="F226" s="1" t="s">
-        <v>208</v>
-      </c>
       <c r="G226" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H226">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I226" t="s">
-        <v>209</v>
+        <v>14</v>
       </c>
     </row>
     <row r="227" spans="1:9" x14ac:dyDescent="0.25">
@@ -7748,10 +7757,10 @@
         <v>208</v>
       </c>
       <c r="G227" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H227">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I227" t="s">
         <v>209</v>
@@ -7759,31 +7768,31 @@
     </row>
     <row r="228" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A228">
-        <v>11508</v>
+        <v>11507</v>
       </c>
       <c r="B228" t="s">
         <v>205</v>
       </c>
       <c r="C228">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D228">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E228" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="F228" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="F228" s="1" t="s">
-        <v>211</v>
-      </c>
       <c r="G228" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H228">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I228" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="229" spans="1:9" x14ac:dyDescent="0.25">
@@ -7806,10 +7815,10 @@
         <v>211</v>
       </c>
       <c r="G229" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H229">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I229" t="s">
         <v>210</v>
@@ -7817,31 +7826,31 @@
     </row>
     <row r="230" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A230">
-        <v>11509</v>
+        <v>11508</v>
       </c>
       <c r="B230" t="s">
         <v>205</v>
       </c>
       <c r="C230">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D230">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E230" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="F230" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="F230" s="1" t="s">
-        <v>237</v>
-      </c>
       <c r="G230" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H230">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I230" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="231" spans="1:9" x14ac:dyDescent="0.25">
@@ -7864,10 +7873,10 @@
         <v>237</v>
       </c>
       <c r="G231" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H231">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I231" t="s">
         <v>212</v>
@@ -7893,10 +7902,10 @@
         <v>237</v>
       </c>
       <c r="G232" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H232">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I232" t="s">
         <v>212</v>
@@ -7904,31 +7913,31 @@
     </row>
     <row r="233" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A233">
-        <v>11510</v>
+        <v>11509</v>
       </c>
       <c r="B233" t="s">
         <v>205</v>
       </c>
       <c r="C233">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D233">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E233" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="F233" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="F233" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="G233" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="H233">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I233" t="s">
-        <v>238</v>
+        <v>212</v>
       </c>
     </row>
     <row r="234" spans="1:9" x14ac:dyDescent="0.25">
@@ -7948,13 +7957,13 @@
         <v>237</v>
       </c>
       <c r="F234" s="1" t="s">
-        <v>24</v>
+        <v>271</v>
       </c>
       <c r="G234" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H234">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I234" t="s">
         <v>238</v>
@@ -7977,13 +7986,13 @@
         <v>237</v>
       </c>
       <c r="F235" s="1" t="s">
-        <v>24</v>
+        <v>271</v>
       </c>
       <c r="G235" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="H235">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I235" t="s">
         <v>238</v>
@@ -7991,602 +8000,602 @@
     </row>
     <row r="236" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A236">
-        <v>11626</v>
+        <v>11510</v>
       </c>
       <c r="B236" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="C236">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D236">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>9</v>
+        <v>237</v>
       </c>
       <c r="F236" s="1" t="s">
-        <v>214</v>
+        <v>271</v>
       </c>
       <c r="G236" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H236">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I236" t="s">
-        <v>14</v>
+        <v>238</v>
       </c>
     </row>
     <row r="237" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A237">
-        <v>11626</v>
+        <v>11511</v>
       </c>
       <c r="B237" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="C237">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D237">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="E237" s="1" t="s">
-        <v>9</v>
+        <v>271</v>
       </c>
       <c r="F237" s="1" t="s">
-        <v>214</v>
+        <v>24</v>
       </c>
       <c r="G237" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H237">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I237" t="s">
-        <v>14</v>
+        <v>272</v>
       </c>
     </row>
     <row r="238" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A238">
-        <v>11627</v>
+        <v>11511</v>
       </c>
       <c r="B238" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="C238">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D238">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="E238" s="1" t="s">
-        <v>214</v>
+        <v>271</v>
       </c>
       <c r="F238" s="1" t="s">
-        <v>215</v>
+        <v>24</v>
       </c>
       <c r="G238" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H238">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I238" t="s">
-        <v>216</v>
+        <v>272</v>
       </c>
     </row>
     <row r="239" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A239">
-        <v>11627</v>
+        <v>11511</v>
       </c>
       <c r="B239" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="C239">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D239">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="E239" s="1" t="s">
-        <v>214</v>
+        <v>271</v>
       </c>
       <c r="F239" s="1" t="s">
-        <v>215</v>
+        <v>24</v>
       </c>
       <c r="G239" t="s">
         <v>11</v>
       </c>
       <c r="H239">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I239" t="s">
-        <v>216</v>
+        <v>272</v>
       </c>
     </row>
     <row r="240" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A240">
-        <v>11628</v>
+        <v>11626</v>
       </c>
       <c r="B240" t="s">
         <v>213</v>
       </c>
       <c r="C240">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D240">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E240" s="1" t="s">
-        <v>215</v>
+        <v>9</v>
       </c>
       <c r="F240" s="1" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="G240" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H240">
         <v>5</v>
       </c>
       <c r="I240" t="s">
-        <v>219</v>
+        <v>14</v>
       </c>
     </row>
     <row r="241" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A241">
-        <v>11628</v>
+        <v>11626</v>
       </c>
       <c r="B241" t="s">
         <v>213</v>
       </c>
       <c r="C241">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D241">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E241" s="1" t="s">
-        <v>215</v>
+        <v>9</v>
       </c>
       <c r="F241" s="1" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="G241" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H241">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I241" t="s">
-        <v>219</v>
+        <v>14</v>
       </c>
     </row>
     <row r="242" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A242">
-        <v>11628</v>
+        <v>11627</v>
       </c>
       <c r="B242" t="s">
         <v>213</v>
       </c>
       <c r="C242">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D242">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E242" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="F242" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="F242" s="1" t="s">
-        <v>217</v>
-      </c>
       <c r="G242" t="s">
-        <v>218</v>
+        <v>10</v>
       </c>
       <c r="H242">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I242" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
     <row r="243" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A243">
-        <v>11629</v>
+        <v>11627</v>
       </c>
       <c r="B243" t="s">
         <v>213</v>
       </c>
       <c r="C243">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D243">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E243" s="1" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F243" s="1" t="s">
-        <v>243</v>
+        <v>215</v>
       </c>
       <c r="G243" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H243">
         <v>4</v>
       </c>
       <c r="I243" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="244" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A244">
-        <v>11629</v>
+        <v>11628</v>
       </c>
       <c r="B244" t="s">
         <v>213</v>
       </c>
       <c r="C244">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D244">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E244" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="F244" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="F244" s="1" t="s">
-        <v>243</v>
-      </c>
       <c r="G244" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H244">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I244" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="245" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A245">
-        <v>11629</v>
+        <v>11628</v>
       </c>
       <c r="B245" t="s">
         <v>213</v>
       </c>
       <c r="C245">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D245">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E245" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="F245" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="F245" s="1" t="s">
-        <v>243</v>
-      </c>
       <c r="G245" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="H245">
         <v>2</v>
       </c>
       <c r="I245" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="246" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A246">
-        <v>11630</v>
+        <v>11628</v>
       </c>
       <c r="B246" t="s">
         <v>213</v>
       </c>
       <c r="C246">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D246">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>243</v>
+        <v>215</v>
       </c>
       <c r="F246" s="1" t="s">
-        <v>24</v>
+        <v>217</v>
       </c>
       <c r="G246" t="s">
-        <v>10</v>
+        <v>218</v>
       </c>
       <c r="H246">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I246" t="s">
-        <v>245</v>
+        <v>219</v>
       </c>
     </row>
     <row r="247" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A247">
-        <v>11630</v>
+        <v>11629</v>
       </c>
       <c r="B247" t="s">
         <v>213</v>
       </c>
       <c r="C247">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D247">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E247" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="F247" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="F247" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="G247" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="H247">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I247" t="s">
-        <v>245</v>
+        <v>220</v>
       </c>
     </row>
     <row r="248" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A248">
-        <v>11706</v>
+        <v>11629</v>
       </c>
       <c r="B248" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="C248">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D248">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="F248" s="1" t="s">
-        <v>223</v>
+        <v>243</v>
       </c>
       <c r="G248" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="H248">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="I248" t="s">
-        <v>14</v>
+        <v>220</v>
       </c>
     </row>
     <row r="249" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A249">
-        <v>11707</v>
+        <v>11629</v>
       </c>
       <c r="B249" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="C249">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="D249">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="F249" s="1" t="s">
-        <v>224</v>
+        <v>243</v>
       </c>
       <c r="G249" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H249">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I249" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
     </row>
     <row r="250" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A250">
-        <v>11707</v>
+        <v>11630</v>
       </c>
       <c r="B250" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="C250">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D250">
+        <v>30</v>
+      </c>
+      <c r="E250" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="F250" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G250" t="s">
+        <v>10</v>
+      </c>
+      <c r="H250">
         <v>7</v>
       </c>
-      <c r="E250" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F250" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="G250" t="s">
-        <v>20</v>
-      </c>
-      <c r="H250">
-        <v>4</v>
-      </c>
       <c r="I250" t="s">
-        <v>225</v>
+        <v>245</v>
       </c>
     </row>
     <row r="251" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A251">
-        <v>11708</v>
+        <v>11630</v>
       </c>
       <c r="B251" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="C251">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D251">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>224</v>
+        <v>243</v>
       </c>
       <c r="F251" s="1" t="s">
-        <v>226</v>
+        <v>24</v>
       </c>
       <c r="G251" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="H251">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I251" t="s">
-        <v>227</v>
+        <v>245</v>
       </c>
     </row>
     <row r="252" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A252">
-        <v>11708</v>
+        <v>11706</v>
       </c>
       <c r="B252" t="s">
         <v>221</v>
       </c>
       <c r="C252">
+        <v>4</v>
+      </c>
+      <c r="D252">
         <v>6</v>
       </c>
-      <c r="D252">
-        <v>8</v>
-      </c>
       <c r="E252" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="F252" s="1" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="G252" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H252">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I252" t="s">
-        <v>227</v>
+        <v>14</v>
       </c>
     </row>
     <row r="253" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A253">
-        <v>11708</v>
+        <v>11707</v>
       </c>
       <c r="B253" t="s">
         <v>221</v>
       </c>
       <c r="C253">
+        <v>5</v>
+      </c>
+      <c r="D253">
+        <v>7</v>
+      </c>
+      <c r="E253" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F253" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="G253" t="s">
+        <v>10</v>
+      </c>
+      <c r="H253">
         <v>6</v>
       </c>
-      <c r="D253">
-        <v>8</v>
-      </c>
-      <c r="E253" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="F253" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="G253" t="s">
-        <v>18</v>
-      </c>
-      <c r="H253">
-        <v>2</v>
-      </c>
       <c r="I253" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="254" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A254">
-        <v>11709</v>
+        <v>11707</v>
       </c>
       <c r="B254" t="s">
         <v>221</v>
       </c>
       <c r="C254">
+        <v>5</v>
+      </c>
+      <c r="D254">
         <v>7</v>
       </c>
-      <c r="D254">
-        <v>9</v>
-      </c>
       <c r="E254" s="1" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="F254" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="G254" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="H254">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I254" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
     </row>
     <row r="255" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A255">
-        <v>11710</v>
+        <v>11708</v>
       </c>
       <c r="B255" t="s">
         <v>221</v>
       </c>
       <c r="C255">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D255">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="F255" s="1" t="s">
-        <v>259</v>
+        <v>226</v>
       </c>
       <c r="G255" t="s">
         <v>53</v>
       </c>
       <c r="H255">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I255" t="s">
-        <v>258</v>
+        <v>227</v>
       </c>
     </row>
     <row r="256" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A256">
-        <v>11710</v>
+        <v>11708</v>
       </c>
       <c r="B256" t="s">
         <v>221</v>
       </c>
       <c r="C256">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D256">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E256" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="F256" s="1" t="s">
-        <v>259</v>
+        <v>226</v>
       </c>
       <c r="G256" t="s">
         <v>20</v>
@@ -8595,27 +8604,27 @@
         <v>3</v>
       </c>
       <c r="I256" t="s">
-        <v>258</v>
+        <v>227</v>
       </c>
     </row>
     <row r="257" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A257">
-        <v>11710</v>
+        <v>11708</v>
       </c>
       <c r="B257" t="s">
         <v>221</v>
       </c>
       <c r="C257">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D257">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E257" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="F257" s="1" t="s">
-        <v>259</v>
+        <v>226</v>
       </c>
       <c r="G257" t="s">
         <v>18</v>
@@ -8624,93 +8633,209 @@
         <v>2</v>
       </c>
       <c r="I257" t="s">
-        <v>258</v>
+        <v>227</v>
       </c>
     </row>
     <row r="258" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A258">
-        <v>11711</v>
+        <v>11709</v>
       </c>
       <c r="B258" t="s">
         <v>221</v>
       </c>
       <c r="C258">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D258">
+        <v>9</v>
+      </c>
+      <c r="E258" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="F258" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="G258" t="s">
         <v>11</v>
       </c>
-      <c r="E258" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="F258" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G258" t="s">
-        <v>10</v>
-      </c>
       <c r="H258">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I258" t="s">
-        <v>261</v>
+        <v>229</v>
       </c>
     </row>
     <row r="259" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A259">
-        <v>11711</v>
+        <v>11710</v>
       </c>
       <c r="B259" t="s">
         <v>221</v>
       </c>
       <c r="C259">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D259">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E259" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="F259" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="F259" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="G259" t="s">
-        <v>260</v>
+        <v>53</v>
       </c>
       <c r="H259">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I259" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
     </row>
     <row r="260" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A260">
-        <v>11711</v>
+        <v>11710</v>
       </c>
       <c r="B260" t="s">
         <v>221</v>
       </c>
       <c r="C260">
+        <v>7</v>
+      </c>
+      <c r="D260">
+        <v>10</v>
+      </c>
+      <c r="E260" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="F260" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="G260" t="s">
+        <v>20</v>
+      </c>
+      <c r="H260">
+        <v>3</v>
+      </c>
+      <c r="I260" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A261">
+        <v>11710</v>
+      </c>
+      <c r="B261" t="s">
+        <v>221</v>
+      </c>
+      <c r="C261">
+        <v>7</v>
+      </c>
+      <c r="D261">
+        <v>10</v>
+      </c>
+      <c r="E261" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="F261" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="G261" t="s">
+        <v>18</v>
+      </c>
+      <c r="H261">
+        <v>2</v>
+      </c>
+      <c r="I261" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A262">
+        <v>11711</v>
+      </c>
+      <c r="B262" t="s">
+        <v>221</v>
+      </c>
+      <c r="C262">
         <v>8</v>
       </c>
-      <c r="D260">
+      <c r="D262">
         <v>11</v>
       </c>
-      <c r="E260" s="1" t="s">
+      <c r="E262" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="F260" s="1" t="s">
+      <c r="F262" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G260" t="s">
-        <v>20</v>
-      </c>
-      <c r="H260">
+      <c r="G262" t="s">
+        <v>10</v>
+      </c>
+      <c r="H262">
+        <v>5</v>
+      </c>
+      <c r="I262" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A263">
+        <v>11711</v>
+      </c>
+      <c r="B263" t="s">
+        <v>221</v>
+      </c>
+      <c r="C263">
+        <v>8</v>
+      </c>
+      <c r="D263">
+        <v>11</v>
+      </c>
+      <c r="E263" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="F263" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G263" t="s">
+        <v>260</v>
+      </c>
+      <c r="H263">
+        <v>3</v>
+      </c>
+      <c r="I263" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A264">
+        <v>11711</v>
+      </c>
+      <c r="B264" t="s">
+        <v>221</v>
+      </c>
+      <c r="C264">
+        <v>8</v>
+      </c>
+      <c r="D264">
+        <v>11</v>
+      </c>
+      <c r="E264" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="F264" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G264" t="s">
+        <v>20</v>
+      </c>
+      <c r="H264">
         <v>2</v>
       </c>
-      <c r="I260" t="s">
+      <c r="I264" t="s">
         <v>261</v>
       </c>
     </row>
